--- a/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/20,08,26 ПОКОМ КИ/дв 20,08,26 днрсч пок ки.xlsx
+++ b/2026/ЗАВОДЫ/ПОКОМ/филиалы НВ/08,26/20,08,26 ПОКОМ КИ/дв 20,08,26 днрсч пок ки.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\20,08,26 ПОКОМ КИ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\ПОКОМ\филиалы НВ\08,26\20,08,26 ПОКОМ КИ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09B64D65-DB12-4042-B2A9-9A08BCFC5241}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CEC271B4-1C58-40BD-810D-A0E8101A373B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,15 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet!$A$3:$AQ$137</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -1301,11 +1309,8 @@
 </file>
 
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:absoluteUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Лист1"/>
     </sheetNames>
@@ -1378,7 +1383,7 @@
 </file>
 
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Sheet"/>
@@ -17074,7 +17079,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:AQ500"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -17544,7 +17548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>41</v>
       </c>
@@ -17663,7 +17667,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>45</v>
       </c>
@@ -17783,7 +17787,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>47</v>
       </c>
@@ -17906,7 +17910,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>49</v>
       </c>
@@ -18019,7 +18023,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="10" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
         <v>53</v>
       </c>
@@ -18148,7 +18152,7 @@
         <v>SU001718</v>
       </c>
     </row>
-    <row r="11" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>57</v>
       </c>
@@ -18272,7 +18276,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="12" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>60</v>
       </c>
@@ -18388,7 +18392,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="13" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>62</v>
       </c>
@@ -18504,7 +18508,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>64</v>
       </c>
@@ -18620,7 +18624,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="15" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A15" s="9" t="s">
         <v>66</v>
       </c>
@@ -18731,7 +18735,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="16" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A16" s="23" t="s">
         <v>70</v>
       </c>
@@ -18980,7 +18984,7 @@
         <v>SU000126</v>
       </c>
     </row>
-    <row r="18" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>74</v>
       </c>
@@ -19096,7 +19100,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="19" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A19" s="9" t="s">
         <v>76</v>
       </c>
@@ -19209,7 +19213,7 @@
         <v>SU004238</v>
       </c>
     </row>
-    <row r="20" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A20" s="9" t="s">
         <v>79</v>
       </c>
@@ -19310,7 +19314,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="21" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>82</v>
       </c>
@@ -19423,7 +19427,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="22" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>85</v>
       </c>
@@ -19540,7 +19544,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="23" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A23" s="9" t="s">
         <v>87</v>
       </c>
@@ -19653,7 +19657,7 @@
         <v>SU003422</v>
       </c>
     </row>
-    <row r="24" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>90</v>
       </c>
@@ -19768,7 +19772,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="25" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>92</v>
       </c>
@@ -19888,7 +19892,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="26" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A26" s="9" t="s">
         <v>94</v>
       </c>
@@ -19989,7 +19993,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="27" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>96</v>
       </c>
@@ -20109,7 +20113,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="28" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>98</v>
       </c>
@@ -20220,7 +20224,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="29" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A29" s="9" t="s">
         <v>101</v>
       </c>
@@ -20321,7 +20325,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="30" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A30" s="9" t="s">
         <v>103</v>
       </c>
@@ -20422,7 +20426,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="31" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>105</v>
       </c>
@@ -20544,7 +20548,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A32" s="9" t="s">
         <v>108</v>
       </c>
@@ -20649,7 +20653,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>110</v>
       </c>
@@ -20773,7 +20777,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="34" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A34" s="9" t="s">
         <v>112</v>
       </c>
@@ -20874,7 +20878,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A35" s="9" t="s">
         <v>114</v>
       </c>
@@ -20975,7 +20979,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A36" s="9" t="s">
         <v>116</v>
       </c>
@@ -21076,7 +21080,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="37" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A37" s="9" t="s">
         <v>118</v>
       </c>
@@ -21177,7 +21181,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="38" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>120</v>
       </c>
@@ -21301,7 +21305,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>122</v>
       </c>
@@ -21422,7 +21426,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>125</v>
       </c>
@@ -21542,7 +21546,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>127</v>
       </c>
@@ -21664,7 +21668,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>129</v>
       </c>
@@ -21776,7 +21780,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="43" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
         <v>132</v>
       </c>
@@ -21890,7 +21894,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="44" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>134</v>
       </c>
@@ -22010,7 +22014,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="45" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>136</v>
       </c>
@@ -22124,7 +22128,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>138</v>
       </c>
@@ -22240,7 +22244,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>140</v>
       </c>
@@ -22358,7 +22362,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>142</v>
       </c>
@@ -22472,7 +22476,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>144</v>
       </c>
@@ -22600,7 +22604,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>146</v>
       </c>
@@ -22718,7 +22722,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>148</v>
       </c>
@@ -22833,7 +22837,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>150</v>
       </c>
@@ -22948,7 +22952,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A53" s="9" t="s">
         <v>152</v>
       </c>
@@ -23049,7 +23053,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="54" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A54" s="23" t="s">
         <v>154</v>
       </c>
@@ -23173,7 +23177,7 @@
         <v>SU002815</v>
       </c>
     </row>
-    <row r="55" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>156</v>
       </c>
@@ -23291,7 +23295,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="56" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A56" s="9" t="s">
         <v>158</v>
       </c>
@@ -23392,7 +23396,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="57" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>160</v>
       </c>
@@ -23503,7 +23507,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="58" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A58" s="23" t="s">
         <v>162</v>
       </c>
@@ -23627,7 +23631,7 @@
         <v>SU002829</v>
       </c>
     </row>
-    <row r="59" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>164</v>
       </c>
@@ -23741,7 +23745,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="60" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>166</v>
       </c>
@@ -23857,7 +23861,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="61" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>168</v>
       </c>
@@ -23968,7 +23972,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="62" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>170</v>
       </c>
@@ -24082,7 +24086,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="63" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>172</v>
       </c>
@@ -24195,7 +24199,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="64" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>174</v>
       </c>
@@ -24313,7 +24317,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="65" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>177</v>
       </c>
@@ -24431,7 +24435,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="66" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>179</v>
       </c>
@@ -24549,7 +24553,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="67" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>181</v>
       </c>
@@ -24669,7 +24673,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="68" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>183</v>
       </c>
@@ -24785,7 +24789,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="69" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>185</v>
       </c>
@@ -24898,7 +24902,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="70" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>187</v>
       </c>
@@ -25016,7 +25020,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="71" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>189</v>
       </c>
@@ -25132,7 +25136,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="72" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A72" s="9" t="s">
         <v>191</v>
       </c>
@@ -25233,7 +25237,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="73" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>193</v>
       </c>
@@ -25347,7 +25351,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="74" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A74" s="9" t="s">
         <v>195</v>
       </c>
@@ -25449,7 +25453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>196</v>
       </c>
@@ -25565,7 +25569,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="76" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>198</v>
       </c>
@@ -25681,7 +25685,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="77" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>200</v>
       </c>
@@ -25786,7 +25790,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="78" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A78" s="9" t="s">
         <v>203</v>
       </c>
@@ -25891,7 +25895,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="79" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
         <v>205</v>
       </c>
@@ -26002,7 +26006,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="80" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>207</v>
       </c>
@@ -26116,7 +26120,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="81" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>209</v>
       </c>
@@ -26232,7 +26236,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="82" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>212</v>
       </c>
@@ -26348,7 +26352,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="83" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>214</v>
       </c>
@@ -26462,7 +26466,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="84" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>216</v>
       </c>
@@ -26580,7 +26584,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="85" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>218</v>
       </c>
@@ -26700,7 +26704,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="86" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A86" s="9" t="s">
         <v>220</v>
       </c>
@@ -26802,7 +26806,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>221</v>
       </c>
@@ -26913,7 +26917,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="88" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>223</v>
       </c>
@@ -27024,7 +27028,7 @@
         <v>224</v>
       </c>
     </row>
-    <row r="89" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A89" s="9" t="s">
         <v>225</v>
       </c>
@@ -27125,7 +27129,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="90" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A90" s="23" t="s">
         <v>227</v>
       </c>
@@ -27248,7 +27252,7 @@
         <v>SU002634</v>
       </c>
     </row>
-    <row r="91" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>229</v>
       </c>
@@ -27364,7 +27368,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="92" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A92" s="23" t="s">
         <v>231</v>
       </c>
@@ -27733,7 +27737,7 @@
         <v>SU003422</v>
       </c>
     </row>
-    <row r="95" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>235</v>
       </c>
@@ -27847,7 +27851,7 @@
         <v>236</v>
       </c>
     </row>
-    <row r="96" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A96" s="9" t="s">
         <v>237</v>
       </c>
@@ -27950,7 +27954,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="97" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A97" s="9" t="s">
         <v>239</v>
       </c>
@@ -28050,7 +28054,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>240</v>
       </c>
@@ -28166,7 +28170,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="99" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>242</v>
       </c>
@@ -28279,7 +28283,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="100" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>244</v>
       </c>
@@ -28395,7 +28399,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="101" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>247</v>
       </c>
@@ -28514,7 +28518,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="102" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>250</v>
       </c>
@@ -28630,7 +28634,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="103" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A103" s="9" t="s">
         <v>252</v>
       </c>
@@ -28739,7 +28743,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="104" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>254</v>
       </c>
@@ -28853,7 +28857,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="105" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>256</v>
       </c>
@@ -28967,7 +28971,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="106" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>258</v>
       </c>
@@ -29086,7 +29090,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="107" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A107" s="9" t="s">
         <v>260</v>
       </c>
@@ -29187,7 +29191,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="108" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>262</v>
       </c>
@@ -29303,7 +29307,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="109" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>265</v>
       </c>
@@ -29422,7 +29426,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="110" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>268</v>
       </c>
@@ -29541,7 +29545,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="111" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>270</v>
       </c>
@@ -29660,7 +29664,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="112" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>272</v>
       </c>
@@ -29777,7 +29781,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="113" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>274</v>
       </c>
@@ -29901,7 +29905,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="114" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>276</v>
       </c>
@@ -30015,7 +30019,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="115" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>278</v>
       </c>
@@ -30128,7 +30132,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="116" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>280</v>
       </c>
@@ -30247,7 +30251,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="117" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>282</v>
       </c>
@@ -30369,7 +30373,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="118" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>284</v>
       </c>
@@ -30489,7 +30493,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="119" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>286</v>
       </c>
@@ -30608,7 +30612,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="120" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A120" s="9" t="s">
         <v>289</v>
       </c>
@@ -30710,7 +30714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>290</v>
       </c>
@@ -30821,7 +30825,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="122" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>292</v>
       </c>
@@ -30930,7 +30934,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="123" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>294</v>
       </c>
@@ -31046,7 +31050,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="124" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>297</v>
       </c>
@@ -31162,7 +31166,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="125" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="s">
         <v>299</v>
       </c>
@@ -31275,7 +31279,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="126" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>302</v>
       </c>
@@ -31390,7 +31394,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="127" spans="1:43" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:43" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>304</v>
       </c>
@@ -31631,7 +31635,7 @@
         <v>SU004238</v>
       </c>
     </row>
-    <row r="129" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>307</v>
       </c>
@@ -31747,7 +31751,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="130" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>310</v>
       </c>
@@ -31860,7 +31864,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="131" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>312</v>
       </c>
@@ -31971,7 +31975,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="132" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>314</v>
       </c>
@@ -32089,7 +32093,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="133" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>316</v>
       </c>
@@ -32207,7 +32211,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="134" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>318</v>
       </c>
@@ -32321,7 +32325,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="135" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>320</v>
       </c>
@@ -32437,7 +32441,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="136" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>322</v>
       </c>
@@ -32551,7 +32555,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="137" spans="1:42" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A137" s="9" t="s">
         <v>324</v>
       </c>
@@ -48267,18 +48271,7 @@
       <c r="AO500" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:AQ137" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="21">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-    <filterColumn colId="42">
-      <customFilters>
-        <customFilter operator="notEqual" val=" "/>
-      </customFilters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A3:AQ137" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" verticalDpi="0"/>
 </worksheet>
